--- a/InputData/elec/BBPPRTY/BAU Ban Power Plant Retrofits This Year.xlsx
+++ b/InputData/elec/BBPPRTY/BAU Ban Power Plant Retrofits This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BBPPRTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\FL\elec\BBPPRTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90DEBFF-EF90-4038-9856-5C954E6DA2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A61E70AF-9735-4AE0-8301-B4A19237809E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Source:</t>
   </si>
@@ -53,9 +53,6 @@
     <t>nuclear</t>
   </si>
   <si>
-    <t>Max Potential Capacity (MW)</t>
-  </si>
-  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -138,6 +135,21 @@
   </si>
   <si>
     <t>We do not allow CCS retrofits before 2028, aligned with NREL's approach.</t>
+  </si>
+  <si>
+    <t>We already include all coal CCS retrofits projected by EPA as part of its 111 rules.</t>
+  </si>
+  <si>
+    <t>Projected coal retriements and retrofits cover all of the exisiting coal fleet between</t>
+  </si>
+  <si>
+    <t>2028 and 2035, so we do not allow any additional retrofits.</t>
+  </si>
+  <si>
+    <t>% of capacity available for retrofit</t>
+  </si>
+  <si>
+    <t>Florida</t>
   </si>
 </sst>
 </file>
@@ -203,7 +215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -215,6 +227,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -520,63 +533,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="60.85546875" customWidth="1"/>
+    <col min="2" max="2" width="60.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="7">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B6" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B8" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -591,15 +625,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="1" max="1" width="26.3984375" customWidth="1"/>
+    <col min="2" max="2" width="27.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -692,9 +726,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
@@ -787,105 +821,105 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>0</v>
+      </c>
+      <c r="W3" s="5">
+        <v>0</v>
+      </c>
+      <c r="X3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="5">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>0</v>
-      </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5">
-        <v>0</v>
-      </c>
-      <c r="T3" s="5">
-        <v>0</v>
-      </c>
-      <c r="U3" s="5">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5">
-        <v>0</v>
-      </c>
-      <c r="W3" s="5">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
       <c r="B4" s="5">
         <v>0</v>
       </c>
@@ -977,7 +1011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1072,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1167,9 +1201,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -1262,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1357,7 +1391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1452,7 +1486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1547,295 +1581,295 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5">
-        <v>0</v>
-      </c>
-      <c r="N11" s="5">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5">
-        <v>0</v>
-      </c>
-      <c r="U11" s="5">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5">
-        <v>0</v>
-      </c>
-      <c r="W11" s="5">
-        <v>0</v>
-      </c>
-      <c r="X11" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="5">
-        <v>0</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5">
-        <v>0</v>
-      </c>
-      <c r="W12" s="5">
-        <v>0</v>
-      </c>
-      <c r="X12" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0</v>
+      </c>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
+      <c r="X13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0</v>
-      </c>
-      <c r="L13" s="5">
-        <v>0</v>
-      </c>
-      <c r="M13" s="5">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5">
-        <v>0</v>
-      </c>
-      <c r="O13" s="5">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5">
-        <v>0</v>
-      </c>
-      <c r="S13" s="5">
-        <v>0</v>
-      </c>
-      <c r="T13" s="5">
-        <v>0</v>
-      </c>
-      <c r="U13" s="5">
-        <v>0</v>
-      </c>
-      <c r="V13" s="5">
-        <v>0</v>
-      </c>
-      <c r="W13" s="5">
-        <v>0</v>
-      </c>
-      <c r="X13" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
       <c r="B14" s="5">
         <v>0</v>
       </c>
@@ -1927,295 +1961,295 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>0</v>
+      </c>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
+      <c r="X15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="5">
-        <v>0</v>
-      </c>
-      <c r="C15" s="5">
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5">
-        <v>0</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5">
-        <v>0</v>
-      </c>
-      <c r="L15" s="5">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5">
-        <v>0</v>
-      </c>
-      <c r="P15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5">
-        <v>0</v>
-      </c>
-      <c r="R15" s="5">
-        <v>0</v>
-      </c>
-      <c r="S15" s="5">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5">
-        <v>0</v>
-      </c>
-      <c r="U15" s="5">
-        <v>0</v>
-      </c>
-      <c r="V15" s="5">
-        <v>0</v>
-      </c>
-      <c r="W15" s="5">
-        <v>0</v>
-      </c>
-      <c r="X15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5">
+        <v>0</v>
+      </c>
+      <c r="X16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5">
-        <v>0</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5">
-        <v>0</v>
-      </c>
-      <c r="R16" s="5">
-        <v>0</v>
-      </c>
-      <c r="S16" s="5">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5">
-        <v>0</v>
-      </c>
-      <c r="U16" s="5">
-        <v>0</v>
-      </c>
-      <c r="V16" s="5">
-        <v>0</v>
-      </c>
-      <c r="W16" s="5">
-        <v>0</v>
-      </c>
-      <c r="X16" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="5">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5">
-        <v>0</v>
-      </c>
-      <c r="N17" s="5">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5">
-        <v>0</v>
-      </c>
-      <c r="P17" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5">
-        <v>0</v>
-      </c>
-      <c r="R17" s="5">
-        <v>0</v>
-      </c>
-      <c r="S17" s="5">
-        <v>0</v>
-      </c>
-      <c r="T17" s="5">
-        <v>0</v>
-      </c>
-      <c r="U17" s="5">
-        <v>0</v>
-      </c>
-      <c r="V17" s="5">
-        <v>0</v>
-      </c>
-      <c r="W17" s="5">
-        <v>0</v>
-      </c>
-      <c r="X17" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
       <c r="B18" s="5">
         <v>0</v>
       </c>
@@ -2307,579 +2341,579 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5">
+        <v>0</v>
+      </c>
+      <c r="X19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="5">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5">
-        <v>1</v>
-      </c>
-      <c r="F19" s="5">
-        <v>1</v>
-      </c>
-      <c r="G19" s="5">
-        <v>1</v>
-      </c>
-      <c r="H19" s="5">
-        <v>1</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5">
-        <v>0</v>
-      </c>
-      <c r="L19" s="5">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>0</v>
-      </c>
-      <c r="R19" s="5">
-        <v>0</v>
-      </c>
-      <c r="S19" s="5">
-        <v>0</v>
-      </c>
-      <c r="T19" s="5">
-        <v>0</v>
-      </c>
-      <c r="U19" s="5">
-        <v>0</v>
-      </c>
-      <c r="V19" s="5">
-        <v>0</v>
-      </c>
-      <c r="W19" s="5">
-        <v>0</v>
-      </c>
-      <c r="X19" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" s="5">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+      <c r="J20" s="5">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5">
+        <v>0</v>
+      </c>
+      <c r="X20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="5">
-        <v>1</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1</v>
-      </c>
-      <c r="F20" s="5">
-        <v>1</v>
-      </c>
-      <c r="G20" s="5">
-        <v>1</v>
-      </c>
-      <c r="H20" s="5">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5">
-        <v>0</v>
-      </c>
-      <c r="S20" s="5">
-        <v>0</v>
-      </c>
-      <c r="T20" s="5">
-        <v>0</v>
-      </c>
-      <c r="U20" s="5">
-        <v>0</v>
-      </c>
-      <c r="V20" s="5">
-        <v>0</v>
-      </c>
-      <c r="W20" s="5">
-        <v>0</v>
-      </c>
-      <c r="X20" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5">
+        <v>1</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
+      <c r="R21" s="5">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5">
+        <v>0</v>
+      </c>
+      <c r="W21" s="5">
+        <v>0</v>
+      </c>
+      <c r="X21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1</v>
-      </c>
-      <c r="F21" s="5">
-        <v>1</v>
-      </c>
-      <c r="G21" s="5">
-        <v>1</v>
-      </c>
-      <c r="H21" s="5">
-        <v>1</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5">
-        <v>0</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0</v>
-      </c>
-      <c r="M21" s="5">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5">
-        <v>0</v>
-      </c>
-      <c r="P21" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>0</v>
-      </c>
-      <c r="R21" s="5">
-        <v>0</v>
-      </c>
-      <c r="S21" s="5">
-        <v>0</v>
-      </c>
-      <c r="T21" s="5">
-        <v>0</v>
-      </c>
-      <c r="U21" s="5">
-        <v>0</v>
-      </c>
-      <c r="V21" s="5">
-        <v>0</v>
-      </c>
-      <c r="W21" s="5">
-        <v>0</v>
-      </c>
-      <c r="X21" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" s="5">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5">
+        <v>0</v>
+      </c>
+      <c r="X22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="5">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5">
-        <v>0</v>
-      </c>
-      <c r="L22" s="5">
-        <v>0</v>
-      </c>
-      <c r="M22" s="5">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5">
-        <v>0</v>
-      </c>
-      <c r="T22" s="5">
-        <v>0</v>
-      </c>
-      <c r="U22" s="5">
-        <v>0</v>
-      </c>
-      <c r="V22" s="5">
-        <v>0</v>
-      </c>
-      <c r="W22" s="5">
-        <v>0</v>
-      </c>
-      <c r="X22" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" s="5">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0</v>
+      </c>
+      <c r="O23" s="5">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
+      <c r="R23" s="5">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5">
+        <v>0</v>
+      </c>
+      <c r="T23" s="5">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0</v>
+      </c>
+      <c r="V23" s="5">
+        <v>0</v>
+      </c>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="5">
-        <v>0</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5">
-        <v>0</v>
-      </c>
-      <c r="I23" s="5">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5">
-        <v>0</v>
-      </c>
-      <c r="L23" s="5">
-        <v>0</v>
-      </c>
-      <c r="M23" s="5">
-        <v>0</v>
-      </c>
-      <c r="N23" s="5">
-        <v>0</v>
-      </c>
-      <c r="O23" s="5">
-        <v>0</v>
-      </c>
-      <c r="P23" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5">
-        <v>0</v>
-      </c>
-      <c r="R23" s="5">
-        <v>0</v>
-      </c>
-      <c r="S23" s="5">
-        <v>0</v>
-      </c>
-      <c r="T23" s="5">
-        <v>0</v>
-      </c>
-      <c r="U23" s="5">
-        <v>0</v>
-      </c>
-      <c r="V23" s="5">
-        <v>0</v>
-      </c>
-      <c r="W23" s="5">
-        <v>0</v>
-      </c>
-      <c r="X23" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="B24" s="5">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5">
+        <v>0</v>
+      </c>
+      <c r="W24" s="5">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A25" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="B24" s="5">
-        <v>0</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5">
-        <v>0</v>
-      </c>
-      <c r="L24" s="5">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5">
-        <v>0</v>
-      </c>
-      <c r="S24" s="5">
-        <v>0</v>
-      </c>
-      <c r="T24" s="5">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5">
-        <v>0</v>
-      </c>
-      <c r="V24" s="5">
-        <v>0</v>
-      </c>
-      <c r="W24" s="5">
-        <v>0</v>
-      </c>
-      <c r="X24" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="B25" s="5">
         <v>0</v>
